--- a/05_Figures/F06_prediction/proteins/trajectory/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/d_mcsa/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -134,52 +134,67 @@
     <t xml:space="preserve">CSTB@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">PAIP1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFN1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGLS@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-C@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSPG2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIP1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFN1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">NDUFA5@T2</t>
   </si>
   <si>
     <t xml:space="preserve">NTPCR@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">PDCD6@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS6KA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM21@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GART@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTT2@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">OXSM@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">PGLS@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS6KA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GART@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6@T2</t>
+    <t xml:space="preserve">PDIA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD3@T2</t>
   </si>
   <si>
     <t xml:space="preserve">RPS4X@T1</t>
@@ -188,19 +203,19 @@
     <t xml:space="preserve">SRSF2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">TALDO1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM21@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD3@T2</t>
+    <t xml:space="preserve">FUBP1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCY@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABP5@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TYMP@T3</t>
@@ -209,361 +224,298 @@
     <t xml:space="preserve">AKT2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">ARHGDIA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCY@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FABP5@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-C@T2</t>
+    <t xml:space="preserve">ALDH1L1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METTL26@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNRD1@T2</t>
   </si>
   <si>
     <t xml:space="preserve">PPIA@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">USP5@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADH5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH7A1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX6@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPAT3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM143@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANX@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPD@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPIL3@T1</t>
   </si>
   <si>
+    <t xml:space="preserve">PRKCQ@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANBP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A12@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCY@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD9@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKBP3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMGB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRAS@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA9@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS13@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">TBCB@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">TXNRD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP5@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADH5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH7A1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM143@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPAT3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTL26@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIC@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANX@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX6@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPD@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCQ@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A12@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCY@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD9@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC4@T3</t>
+    <t xml:space="preserve">ACTR3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIP@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF5@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARM1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARS1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT8@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD63@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLPP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19@T3</t>
   </si>
   <si>
     <t xml:space="preserve">CTBP1@T1</t>
   </si>
   <si>
+    <t xml:space="preserve">DCTN4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX39B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPTOR@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJC19@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPYSL2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3K@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3M@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZR@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBLN5@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">GANAB@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">HMGB1@T3</t>
+    <t xml:space="preserve">GDI2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSR@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTT2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBS1L@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEBP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPRT1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPRT1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFITM1@T3</t>
   </si>
   <si>
     <t xml:space="preserve">KIF5B@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">KRAS@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA9@T2</t>
+    <t xml:space="preserve">MPI@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSN@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTX1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MXRA7@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH9@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYL12B@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS5@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS7@T2</t>
   </si>
   <si>
     <t xml:space="preserve">NUDC@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">PFDN5@T3</t>
+    <t xml:space="preserve">NXN@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBPL1A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANK4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEBP1@T3</t>
   </si>
   <si>
     <t xml:space="preserve">PRDX1@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RANBP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS13@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APIP@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APIP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF5@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANX@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARM1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARS1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT8@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD63@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPTOR@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHODH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJC19@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DTNA@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1A1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3K@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3M@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZR@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBLN5@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITM1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAPDH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBE1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSR@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBS1L@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEBP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPRT1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPRT1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFITM1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN2C1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSN@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-ND5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTX1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH9@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYL12B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS5@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS7@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPEPL1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSBPL1A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANK4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEBP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMM2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAB2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA5@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSME1@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RAB1B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB1B@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">RAP1B@T3</t>
   </si>
   <si>
     <t xml:space="preserve">RPL18@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL37A@T2</t>
+    <t xml:space="preserve">RPL37A@T3</t>
   </si>
   <si>
     <t xml:space="preserve">RPS27@T3</t>
@@ -578,13 +530,10 @@
     <t xml:space="preserve">SEC22B@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">SLC25A13@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMYD2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">SYNCRIP@T2</t>
+    <t xml:space="preserve">SYNGR2@T2</t>
   </si>
   <si>
     <t xml:space="preserve">TIMM21@T2</t>
@@ -596,16 +545,10 @@
     <t xml:space="preserve">TMEM11@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">TXN@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">VAMP2@T3</t>
   </si>
   <si>
     <t xml:space="preserve">VIM@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS4A@T3</t>
   </si>
 </sst>
 </file>
@@ -992,13 +935,13 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.210984082099208</v>
+        <v>0.181522266577792</v>
       </c>
       <c r="I2" t="n">
         <v>0.551648351648352</v>
@@ -1025,29 +968,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.210984082099208</v>
+        <v>0.181522266577792</v>
       </c>
       <c r="I3" t="n">
         <v>0.551648351648352</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.0696517412935323</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.0746268656716418</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.556124962641035</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.560357322860819</v>
-      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1071,2206 +1006,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.780415388137675</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.828504258331457</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.804050958915213</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.301808489789481</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.362034973220037</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.00961322078569848</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.4319156230911</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.07969087011418</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.069029104680709</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.945277967617084</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0431229347193579</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.615336587372379</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.02122903959905</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.07114567259621</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.579388242326605</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.95988312285661</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.766717104045851</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.17677052985211</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.756765111248756</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.51882222413926</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.470399379442745</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.133491849039217</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.22117386210056</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.294539931784907</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.385713350976691</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.446978623903225</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-2.0914311775159</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-1.14317428963556</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.732374279465372</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.68150438035235</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.134074474937706</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.0750737685898282</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.0576039843878757</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.148757110159509</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-1.11223478558226</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.943293756845024</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.739425894165642</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.522156173599674</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.641054881619256</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.272784201342213</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.436922569323341</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.176092732449223</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.307326713788158</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-1.16815196952808</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.0424338173734755</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.348700786638617</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.15174543652203</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.141556088927277</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.0153065516058455</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.06609585867114</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.119359555286048</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.184596316591599</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.14047387963055</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.444536284936379</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.0461121624555028</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.13581891044944</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.409655220462929</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.64387876628309</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.739187513989976</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.0543494575407437</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.26815284258036</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.189086536659285</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.74225883700397</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.59931912807747</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.0275409503626279</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.0789419847064786</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.613488006218054</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.770547938538956</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.227881462805106</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.54588577104685</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-1.2637283845776</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.175385200905675</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.384466250445174</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.217866957331792</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.46233185186966</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.0288810394474841</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.2771703215455</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.0737951951556114</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.928842679387484</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-1.79433822796699</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.305108209471538</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.518454158101682</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.770919218610605</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.69111874270644</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-1.07630066856739</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.287687174846112</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.825794324799201</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.86540676608441</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.356051858172612</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.866517443186019</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.188705692205971</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.121667072196709</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.628242379641343</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.50197112614509</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.373339981182352</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.0577512563412608</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.374054350144965</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.931563528743827</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.914314097181508</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.267044440325785</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0.18593951659893</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.438240001968516</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.1233720796835</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-1.14980072329684</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.880289573303887</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.61125310936639</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0.397110688253257</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.934267811414748</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.120965886808833</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0.232651022125596</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.849478189521934</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.421278865049187</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.667114598371988</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.0246280349979549</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.546999636341215</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.209578304572211</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.138119210305402</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.100735858014454</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.298561823347809</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.804316599199421</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.250314567087959</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.218982766258253</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.831947761310112</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.653573676376114</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.671118901433218</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.00394128993288</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.87852410185191</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-1.092997711938</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.37436278776296</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.130073917026077</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.104739211155665</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-1.25980747567381</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.895063448912602</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.288385388576442</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-2.31676031355254</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.560305479287713</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.34851219247464</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.684204393274273</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0.00441210318341156</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.89265759783705</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-1.01791265114803</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.266996637603492</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.512255258354427</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-1.02883831816576</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.592079403263158</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.12674007066746</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.96640629168044</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.650253963299166</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.512802272306506</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.681303659753136</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-1.01101389509428</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.758686437925139</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.267427514757142</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.553187988736992</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.635655929145855</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>0.358331043901637</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0.217770038715054</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.70798499029524</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.0304309933710669</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.737548345367996</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.323487974433483</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.721109023414667</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.535853669842643</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.957810677663965</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.806799251748287</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.386367254190756</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.170370501213375</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.20155217908866</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.764729212913479</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.524330335144503</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.301546797040679</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.198224511018176</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.27546120521863</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.607585974000712</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.36121662099834</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.0244806542243177</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.412537423681534</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.602493837414221</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.264077663769864</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.0867842802487508</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.38023051787365</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.17769553308794</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.173826403972305</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.5876659784358</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.799140654418566</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.877989320202737</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.738150193323995</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.0191166888706528</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.552394229936257</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-1.00261025181132</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.83286789683041</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.15687731806735</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.815238211492169</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.0748981267330873</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.0356563200329043</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.344114283755971</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.392497547490639</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.998127886709918</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>0.585439809991091</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.0699095473252134</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3313,7 +1048,7 @@
         <v>1.706</v>
       </c>
       <c r="E2" t="n">
-        <v>2.06201927212739</v>
+        <v>2.00983654488007</v>
       </c>
     </row>
     <row r="3">
@@ -3330,7 +1065,7 @@
         <v>4.218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.937794137110563</v>
+        <v>1.02624801069447</v>
       </c>
     </row>
     <row r="4">
@@ -3347,7 +1082,7 @@
         <v>1.578</v>
       </c>
       <c r="E4" t="n">
-        <v>1.43009696357614</v>
+        <v>1.51349503241007</v>
       </c>
     </row>
     <row r="5">
@@ -3364,7 +1099,7 @@
         <v>3.683</v>
       </c>
       <c r="E5" t="n">
-        <v>3.38281924089654</v>
+        <v>3.43006660327624</v>
       </c>
     </row>
     <row r="6">
@@ -3381,7 +1116,7 @@
         <v>2.983</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0986668690649</v>
+        <v>3.03187579189378</v>
       </c>
     </row>
     <row r="7">
@@ -3398,7 +1133,7 @@
         <v>2.44</v>
       </c>
       <c r="E7" t="n">
-        <v>1.18947963740757</v>
+        <v>1.10506842448382</v>
       </c>
     </row>
     <row r="8">
@@ -3415,7 +1150,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>0.887394662767264</v>
+        <v>0.816631866010956</v>
       </c>
     </row>
     <row r="9">
@@ -3432,7 +1167,7 @@
         <v>-1.918</v>
       </c>
       <c r="E9" t="n">
-        <v>0.852294013334425</v>
+        <v>0.814529598848279</v>
       </c>
     </row>
     <row r="10">
@@ -3449,7 +1184,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.51430134064923</v>
+        <v>2.51607338219112</v>
       </c>
     </row>
     <row r="11">
@@ -3466,7 +1201,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199774334418194</v>
+        <v>0.295573154338814</v>
       </c>
     </row>
     <row r="12">
@@ -3483,7 +1218,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0260442118428</v>
+        <v>1.80386178162475</v>
       </c>
     </row>
     <row r="13">
@@ -3500,7 +1235,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3069964997703</v>
+        <v>1.21984465135344</v>
       </c>
     </row>
     <row r="14">
@@ -3517,7 +1252,7 @@
         <v>1.311</v>
       </c>
       <c r="E14" t="n">
-        <v>1.32134325019776</v>
+        <v>1.23972555377934</v>
       </c>
     </row>
     <row r="15">
@@ -3534,7 +1269,7 @@
         <v>2.862</v>
       </c>
       <c r="E15" t="n">
-        <v>1.92657432593569</v>
+        <v>1.56996663097069</v>
       </c>
     </row>
   </sheetData>
@@ -3576,10 +1311,10 @@
         <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -3593,10 +1328,10 @@
         <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -3610,10 +1345,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -3627,10 +1362,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -3644,10 +1379,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="7">
@@ -3695,10 +1430,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -3712,10 +1447,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="11">
@@ -3729,10 +1464,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="12">
@@ -3746,10 +1481,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="13">
@@ -3763,10 +1498,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -3780,10 +1515,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="15">
@@ -3797,10 +1532,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="16">
@@ -3882,10 +1617,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="21">
@@ -3899,10 +1634,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="22">
@@ -3916,10 +1651,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="23">
@@ -3933,10 +1668,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="24">
@@ -4001,10 +1736,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="28">
@@ -4018,10 +1753,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="29">
@@ -4035,10 +1770,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="30">
@@ -4052,10 +1787,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="31">
@@ -4103,10 +1838,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -4120,10 +1855,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -4137,10 +1872,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -4171,10 +1906,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="38">
@@ -4273,10 +2008,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="44">
@@ -4290,10 +2025,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="45">
@@ -4749,10 +2484,10 @@
         <v>106</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="72">
@@ -4766,10 +2501,10 @@
         <v>107</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="73">
@@ -4783,10 +2518,10 @@
         <v>108</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="74">
@@ -5959,329 +3694,6 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="s">
-        <v>178</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>179</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="s">
-        <v>180</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="s">
-        <v>181</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="s">
-        <v>182</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="s">
-        <v>183</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="s">
-        <v>184</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="s">
-        <v>185</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="s">
-        <v>186</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="s">
-        <v>187</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="s">
-        <v>188</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="s">
-        <v>189</v>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="s">
-        <v>190</v>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="s">
-        <v>191</v>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="s">
-        <v>192</v>
-      </c>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="s">
-        <v>193</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="s">
-        <v>194</v>
-      </c>
-      <c r="D159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="s">
-        <v>195</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="s">
-        <v>196</v>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/trajectory/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/d_mcsa/spls/c_data/results.xlsx
@@ -971,7 +971,7 @@
         <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.181522266577792</v>
@@ -979,10 +979,18 @@
       <c r="I3" t="n">
         <v>0.551648351648352</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.0746268656716418</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0746268656716418</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.577689807812321</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.611491454769448</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1006,6 +1014,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.824334178507304</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.843048224286991</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.800779481272809</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.379779007157924</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.430238469917191</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.105472380209945</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.84288767444691</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.07418400795139</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0703957519553847</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.48910139959592</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0420643409969019</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.489630474079307</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.12400774286281</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.03750914064271</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.590456298948736</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.93669445745814</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.505314397463009</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.245460313716437</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.903624379406624</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.37405170688425</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.456379650710364</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.209727691608949</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.20711863036106</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.356113520756276</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.17091315932801</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.404127040917354</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-2.02807861076135</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.549979029369362</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.788862005440333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.3614556226276</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.314287168110585</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.18756809504686</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.0887886747471764</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.151285416819961</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.13940762555339</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.721125579414679</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.975752044503988</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.443976185410307</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.488645543580456</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.158449659998916</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.525781589414887</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.183302416152306</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.295791322923688</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.05952542325209</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.170892059316418</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.609758991958649</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.10183620430608</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.128112571257116</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.122270767286472</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.13314247072993</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.215798220193936</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.220020385541817</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-3.65850556896411</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.38304191098668</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.0163805131856842</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.12118166477815</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.412013667870651</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.54686111908499</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.29220747274195</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.0185515936020346</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.395052299554353</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.0975100829655269</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.23650250636164</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.463281038525164</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.336863718978012</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0273091729201738</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.457193588848281</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.633922190810587</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.16362319327455</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.500207921962383</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.34720716801038</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.155531636323279</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.479302700461668</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.382424616434556</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.48621037961567</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.0351017547299657</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.09901721577315</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.0438509790599801</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.842052503875595</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.77727478458487</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.323903759327844</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.428371077225913</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.961866524866104</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.25917167393713</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.419918664294051</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.184109314284456</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.910115008020608</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.832881126367137</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.233249506246863</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.05554320767184</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.11799024162089</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.146800557360358</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.679015582231536</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.87968944510964</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.404464082163046</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.0862046290962784</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.31064510880684</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.96235141868627</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.19280423649479</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.296877398553488</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.151902866502973</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.067642745089322</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.12687948268189</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.12140401198812</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.738813278415312</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.40088022546053</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.408396494329202</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.10734112267385</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.138327920333909</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.215858314946823</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.91167328531256</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.381537561593132</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.03123460215871</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.634755407606186</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.369846483656713</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.311352590795601</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.0354285094521198</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.662216970871053</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.126549384723243</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.866270622772896</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.233081945317676</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.179543087998539</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.809866674901438</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.896291413948231</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.599629474154268</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.93777556538162</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.795829647039874</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.871654484938583</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.431597640129243</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.151811242478836</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.382539237102864</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.22520516412907</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.932457419608801</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.29065239635905</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-2.6595980314889</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.538866961238011</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.60207672188628</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.78000158953709</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.0672087134237385</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.57422574934807</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.0397764605628</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.0546458223534623</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.558045622147217</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.996697008292522</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.647311473429863</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.193417241298562</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.78568136478256</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.84706228061702</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.644305781097818</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.601687014348165</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.919038042462892</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.45158040639638</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.526214910527794</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.633634274280753</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.679498941395273</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.310168340899106</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.275915481486655</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.63418345357258</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.121482610822412</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.723389646957673</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.21212384227691</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.674990635887742</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1.547949951262</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.633256979060118</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.638285146717361</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.499762515376994</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.305759238637173</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.587060767574036</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.784492422593027</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.0252807631331289</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.159401622150712</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.261776032986305</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.51476599990122</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.628575092055208</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.13575720838867</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.390725804409119</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.806173456128259</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.38561711233794</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.155139668259732</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.0495657258490836</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.43613474887726</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.06843517719674</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.187295922421327</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.676553069954302</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.522789919187512</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.04707978302549</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.74770752786034</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.13055989153298</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.447830142842039</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-1.0078399428</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.813795010431611</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.173436226459859</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.944701867906706</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.202515874211639</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.0139960104789199</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.257712865659023</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.669485204016931</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.957663670585153</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.788001995320655</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.0146986707491972</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
